--- a/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_str.xlsx
+++ b/data/a_01_mortality_data_processed/fitting_mci_doc_cod/sample_results_str.xlsx
@@ -587,7 +587,11 @@
           <t>SUICIDE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SUICIDE</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>SUICIDE</t>
@@ -697,17 +701,21 @@
           <t>BLUNT FORCE HEAD TRAUMA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>BLUNT FORCE HEAD TRAUMA</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BLUNT FORCE HEAD TRAUMA</t>
-        </is>
-      </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
@@ -721,13 +729,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -740,7 +748,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BLUNT</t>
+          <t>CARDIAC</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -770,22 +778,22 @@
         <v>0</v>
       </c>
       <c r="Y3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -794,7 +802,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>HOMICIDE</t>
+          <t>HEART DISEASE</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1157,23 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HEART - SEVERE ATHERSCLEROTIC &amp; HYPERTENSIVE CV DISEASE
+ DATE OF BIRTH IS ESTIMATED. THE DECEDENT’S AGE AT THE TIME OF DEATH WAS 70. GENDER WAS CODED BY THE PROJECT AS THIS INFORMATION WAS NOT PROVIDED BY DPSC.</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>HEART - SEVERE ATHERSCLEROTIC &amp; HYPERTENSIVE CV DISEASE
+ DATE OF BIRTH IS ESTIMATED. THE DECEDENT’S AGE AT THE TIME OF DEATH WAS 70. GENDER WAS CODED BY THE PROJECT AS THIS INFORMATION WAS NOT PROVIDED BY DPSC.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
@@ -1179,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="b">
         <v>0</v>
@@ -1190,9 +1204,19 @@
       <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>HEART</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>100</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S7" t="b">
         <v>0</v>
       </c>
@@ -1227,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1236,7 +1260,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>HEART DISEASE</t>
         </is>
       </c>
     </row>
@@ -1249,17 +1273,21 @@
           <t>HEP C</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ESLD, HEP C, CIRRHOSIS</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ESLD, HEP C, CIRRHOSIS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>HEP C</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HEP C</t>
-        </is>
-      </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
@@ -1285,14 +1313,24 @@
         <v>0</v>
       </c>
       <c r="N8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CIRRHOSIS</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>100</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S8" t="b">
         <v>0</v>
       </c>
@@ -1318,16 +1356,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="b">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1336,7 +1374,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -1349,17 +1387,21 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CEREBRAL VASCULAR</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CEREBRAL VASCULAR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
@@ -1385,14 +1427,24 @@
         <v>0</v>
       </c>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CEREBRAL VASCULAR ACCIDENT</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Fuzzy</t>
+        </is>
+      </c>
       <c r="S9" t="b">
         <v>0</v>
       </c>
@@ -1418,16 +1470,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="b">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1436,7 +1488,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -1549,10 +1601,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1649,10 +1705,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2151,17 +2211,21 @@
           <t>BLUNT FORCE HEAD INJURIES HOMICIDE</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HOMICIDE-TRAUMATIC BRAIN INJURY</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>HOMICIDE-TRAUMATIC BRAIN INJURY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>BLUNT FORCE HEAD INJURIES HOMICIDE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>BLUNT FORCE HEAD INJURIES HOMICIDE</t>
-        </is>
-      </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2258,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BLUNT</t>
+          <t>TRAUMATIC</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2261,10 +2325,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2471,17 +2539,21 @@
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COVID‐19</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>COVID‐19</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES</t>
-        </is>
-      </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
@@ -2504,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -2512,9 +2584,19 @@
       <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Fuzzy</t>
+        </is>
+      </c>
       <c r="S20" t="b">
         <v>0</v>
       </c>
@@ -2540,16 +2622,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="b">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -2558,7 +2640,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -2671,10 +2753,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2989,17 +3075,21 @@
           <t>METASTATIC UROTHELIAL CARCINOMA OF THE RENAL PELVIS</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CANCER RENAL  W/METS</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>CANCER RENAL  W/METS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>METASTATIC UROTHELIAL CARCINOMA OF THE RENAL PELVIS</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>METASTATIC UROTHELIAL CARCINOMA OF THE RENAL PELVIS</t>
-        </is>
-      </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
@@ -3032,7 +3122,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CARCINOMA</t>
+          <t>CANCER</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3327,17 +3417,21 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DIAABETES MELLITUS</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>DIAABETES MELLITUS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
@@ -3363,14 +3457,24 @@
         <v>0</v>
       </c>
       <c r="N28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>MELLITUS</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>100</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S28" t="b">
         <v>0</v>
       </c>
@@ -3396,16 +3500,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="b">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -3414,7 +3518,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -3845,17 +3949,25 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CANCER.
+ DATE OF BIRTH IS ESTIMATED. THE DECEDENT'S AGE AT THE TIME OF DEATH WAS 56.
+ GENDER WAS CODED BY THE PROJECT AS THIS INFORMATION WAS NOT PROVIDED BY DPSC.</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>CANCER.
+ DATE OF BIRTH IS ESTIMATED. THE DECEDENT'S AGE AT THE TIME OF DEATH WAS 56.
+ GENDER WAS CODED BY THE PROJECT AS THIS INFORMATION WAS NOT PROVIDED BY DPSC.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>MEDICAL</t>
-        </is>
-      </c>
       <c r="F33" t="b">
         <v>0</v>
       </c>
@@ -3881,14 +3993,24 @@
         <v>0</v>
       </c>
       <c r="N33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>100</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S33" t="b">
         <v>0</v>
       </c>
@@ -3914,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="b">
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -3932,7 +4054,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -4059,17 +4181,21 @@
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MALIGNANT NEOPLASMS</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>MALIGNANT NEOPLASMS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES</t>
-        </is>
-      </c>
       <c r="F35" t="b">
         <v>0</v>
       </c>
@@ -4095,14 +4221,24 @@
         <v>0</v>
       </c>
       <c r="N35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>MALIGNANT</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>100</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S35" t="b">
         <v>0</v>
       </c>
@@ -4128,16 +4264,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="b">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4146,7 +4282,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4727,21 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HEPATITIS C</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>HEPATITIS C</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
@@ -4627,14 +4767,24 @@
         <v>0</v>
       </c>
       <c r="N40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>HEPATITIS</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>100</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S40" t="b">
         <v>0</v>
       </c>
@@ -4660,16 +4810,16 @@
         <v>0</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="b">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -4678,7 +4828,7 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -5125,17 +5275,21 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
       <c r="F45" t="b">
         <v>0</v>
       </c>
@@ -5155,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -5166,9 +5320,19 @@
       <c r="O45" t="b">
         <v>0</v>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CARDIAC</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>100</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S45" t="b">
         <v>0</v>
       </c>
@@ -5203,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -5212,7 +5376,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>HEART DISEASE</t>
         </is>
       </c>
     </row>
@@ -5225,17 +5389,21 @@
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DISEASES OF THE HEART</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>DISEASES OF THE HEART</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES</t>
-        </is>
-      </c>
       <c r="F46" t="b">
         <v>0</v>
       </c>
@@ -5255,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
@@ -5266,9 +5434,19 @@
       <c r="O46" t="b">
         <v>0</v>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>HEART</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>100</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S46" t="b">
         <v>0</v>
       </c>
@@ -5303,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -5312,7 +5490,7 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>HEART DISEASE</t>
         </is>
       </c>
     </row>
@@ -5325,10 +5503,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CA LIVER</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>CA LIVER</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5425,10 +5607,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5525,10 +5711,14 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>STAGE LIVER</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>STAGE LIVER</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5625,10 +5815,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5725,17 +5919,21 @@
           <t>RESPIRATORY FAILURE W/HYPOXIA, SEVERE SEPSIS</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>COMPLICATIONS OF SEPSIS, PNEUMONIA</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>COMPLICATIONS OF SEPSIS, PNEUMONIA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>RESPIRATORY FAILURE W/HYPOXIA, SEVERE SEPSIS</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RESPIRATORY FAILURE W/HYPOXIA, SEVERE SEPSIS</t>
-        </is>
-      </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
@@ -5768,7 +5966,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>SEPSIS</t>
+          <t>PNEUMONIA</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -5935,10 +6133,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6135,17 +6337,21 @@
           <t>HEPATOCELLULAR CARCINOMA</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CANCER-LIVER</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>CANCER-LIVER</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>HEPATOCELLULAR CARCINOMA</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>HEPATOCELLULAR CARCINOMA</t>
-        </is>
-      </c>
       <c r="F55" t="b">
         <v>0</v>
       </c>
@@ -6178,7 +6384,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CARCINOMA</t>
+          <t>CANCER</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -6245,17 +6451,21 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LUNG CANCER</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>LUNG CANCER</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
       <c r="F56" t="b">
         <v>0</v>
       </c>
@@ -6281,14 +6491,24 @@
         <v>0</v>
       </c>
       <c r="N56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="b">
         <v>0</v>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>100</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S56" t="b">
         <v>0</v>
       </c>
@@ -6314,16 +6534,16 @@
         <v>0</v>
       </c>
       <c r="AA56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="b">
         <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -6332,7 +6552,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -6445,10 +6665,14 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ACUTE BRONCHOPNEUMONIA</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
+          <t>ACUTE BRONCHOPNEUMONIA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6641,9 +6865,21 @@
         <v>25024</v>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>METASTATIC LUNG CANCER</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>METASTATIC LUNG CANCER</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>METASTATIC LUNG CANCER</t>
+        </is>
+      </c>
       <c r="F60" t="b">
         <v>0</v>
       </c>
@@ -6669,14 +6905,24 @@
         <v>0</v>
       </c>
       <c r="N60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>100</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S60" t="b">
         <v>0</v>
       </c>
@@ -6702,16 +6948,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="b">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -6720,7 +6966,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -6947,17 +7193,21 @@
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>CARDIAC ARREST</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES/ILLNESS</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES/ILLNESS</t>
-        </is>
-      </c>
       <c r="F63" t="b">
         <v>0</v>
       </c>
@@ -6977,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -6988,9 +7238,19 @@
       <c r="O63" t="b">
         <v>0</v>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>CARDIAC</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>100</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S63" t="b">
         <v>0</v>
       </c>
@@ -7025,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -7034,7 +7294,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>HEART DISEASE</t>
         </is>
       </c>
     </row>
@@ -7047,10 +7307,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7673,9 +7937,21 @@
         <v>46023</v>
       </c>
       <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LIVER CANCER</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LIVER CANCER</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LIVER CANCER</t>
+        </is>
+      </c>
       <c r="F70" t="b">
         <v>0</v>
       </c>
@@ -7701,14 +7977,24 @@
         <v>0</v>
       </c>
       <c r="N70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="b">
         <v>0</v>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>100</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S70" t="b">
         <v>0</v>
       </c>
@@ -7734,16 +8020,16 @@
         <v>0</v>
       </c>
       <c r="AA70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="b">
         <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -7752,7 +8038,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -8295,10 +8581,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8509,10 +8799,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8697,94 +8991,108 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ATHEROSCLEROTIC CARDIOVASCULARDISEASE DUE TO HTN</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>ATHEROSCLEROTIC CARDIOVASCULARDISEASE DUE TO HTN</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="b">
+        <v>0</v>
+      </c>
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="b">
+        <v>1</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>ATHEROSCLEROTIC</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>100</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="b">
+        <v>0</v>
+      </c>
+      <c r="U80" t="b">
+        <v>0</v>
+      </c>
+      <c r="V80" t="b">
+        <v>1</v>
+      </c>
+      <c r="W80" t="b">
+        <v>0</v>
+      </c>
+      <c r="X80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE80" t="inlineStr">
         <is>
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="G80" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80" t="b">
-        <v>0</v>
-      </c>
-      <c r="M80" t="b">
-        <v>0</v>
-      </c>
-      <c r="N80" t="b">
-        <v>0</v>
-      </c>
-      <c r="O80" t="b">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="b">
-        <v>0</v>
-      </c>
-      <c r="T80" t="b">
-        <v>0</v>
-      </c>
-      <c r="U80" t="b">
-        <v>0</v>
-      </c>
-      <c r="V80" t="b">
-        <v>1</v>
-      </c>
-      <c r="W80" t="b">
-        <v>0</v>
-      </c>
-      <c r="X80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>99</v>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>HEART DISEASE</t>
         </is>
       </c>
     </row>
@@ -8797,17 +9105,21 @@
           <t>ILLNESS</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>END STAGE LIVER DISEASE HCV</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>END STAGE LIVER DISEASE HCV</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>ILLNESS</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ILLNESS</t>
-        </is>
-      </c>
       <c r="F81" t="b">
         <v>0</v>
       </c>
@@ -8833,14 +9145,24 @@
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="b">
         <v>0</v>
       </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>LIVER DISEASE</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>100</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S81" t="b">
         <v>0</v>
       </c>
@@ -8866,16 +9188,16 @@
         <v>0</v>
       </c>
       <c r="AA81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="b">
         <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -8884,7 +9206,7 @@
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -8897,7 +9219,11 @@
           <t>PENDING INVESTIGATION</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PENDING INVESTIGATION</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>PENDING INVESTIGATION</t>
@@ -8997,10 +9323,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9093,9 +9423,21 @@
         <v>46242</v>
       </c>
       <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LIVER CANCER</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LIVER CANCER</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>LIVER CANCER</t>
+        </is>
+      </c>
       <c r="F84" t="b">
         <v>0</v>
       </c>
@@ -9121,14 +9463,24 @@
         <v>0</v>
       </c>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="b">
         <v>0</v>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>100</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S84" t="b">
         <v>0</v>
       </c>
@@ -9154,16 +9506,16 @@
         <v>0</v>
       </c>
       <c r="AA84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="b">
         <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -9172,7 +9524,7 @@
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -9181,9 +9533,21 @@
         <v>34926</v>
       </c>
       <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SCD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SCD</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SCD</t>
+        </is>
+      </c>
       <c r="F85" t="b">
         <v>0</v>
       </c>
@@ -9597,10 +9961,14 @@
           <t>NATURAL</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NATURAL</t>
+          <t>NOT APPLICABLE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10345,17 +10713,21 @@
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>COVID-19 COMPLICATIONS</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>COVID-19 COMPLICATIONS</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>NATURAL CAUSES</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>NATURAL CAUSES</t>
-        </is>
-      </c>
       <c r="F96" t="b">
         <v>0</v>
       </c>
@@ -10378,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -10386,9 +10758,19 @@
       <c r="O96" t="b">
         <v>0</v>
       </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>100</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S96" t="b">
         <v>0</v>
       </c>
@@ -10414,16 +10796,16 @@
         <v>0</v>
       </c>
       <c r="AA96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="b">
         <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
@@ -10432,7 +10814,7 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>COMMUNICABLE DISEASE</t>
         </is>
       </c>
     </row>
@@ -10555,9 +10937,21 @@
         <v>46090</v>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HANGING</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>HANGING</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>HANGING</t>
+        </is>
+      </c>
       <c r="F98" t="b">
         <v>0</v>
       </c>
@@ -10568,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="b">
         <v>0</v>
@@ -10588,9 +10982,19 @@
       <c r="O98" t="b">
         <v>0</v>
       </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>HANGING</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>100</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
       <c r="S98" t="b">
         <v>0</v>
       </c>
@@ -10610,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="Y98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
       </c>
       <c r="AB98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="b">
         <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
@@ -10634,7 +11038,7 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>UNDETERMINED</t>
+          <t>SUICIDE</t>
         </is>
       </c>
     </row>
